--- a/docs/mezuniyet_bilgileri.xlsx
+++ b/docs/mezuniyet_bilgileri.xlsx
@@ -1,31 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E374AA64-53E9-48DF-B9D7-8CA96865F575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Toplu Sorgulama" sheetId="1" r:id="rId1"/>
+    <sheet name="Toplu Sorgulama" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -36,84 +22,103 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
-    <t>TC KIMLIK NO</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>SOYAD</t>
-  </si>
-  <si>
-    <t>MEZUNIYET TARIHI</t>
-  </si>
-  <si>
-    <t>UNIVERSITE</t>
-  </si>
-  <si>
-    <t>ENSMYOFAK</t>
-  </si>
-  <si>
-    <t>PROGRAM</t>
-  </si>
-  <si>
-    <t>NOTU</t>
-  </si>
-  <si>
-    <t>DURUMU</t>
-  </si>
-  <si>
-    <t>ALİ</t>
-  </si>
-  <si>
-    <t>AKTAŞ</t>
-  </si>
-  <si>
-    <t>03/01/2022</t>
-  </si>
-  <si>
-    <t>İSTANBUL TEKNİK ÜNİVERSİTESİ</t>
-  </si>
-  <si>
-    <t>ELEKTRİK-ELEKTRONİK FAKÜLTESİ</t>
-  </si>
-  <si>
-    <t>ELEKTRONİK VE HABERLEŞME MÜHENDİSLİĞİ (İNGİLİZCE) - ÖRGÜN ÖĞRETİM</t>
-  </si>
-  <si>
-    <t>2.54 / 4.0</t>
-  </si>
-  <si>
-    <t>KAYDI SİLİNMİŞTİR. (AYRILAN ÖĞRENCİLER) - MEZUNİYET</t>
-  </si>
-  <si>
-    <t>24/06/2022</t>
-  </si>
-  <si>
-    <t>BOĞAZİÇİ ÜNİVERSİTESİ</t>
-  </si>
-  <si>
-    <t>FEN-EDEBİYAT FAKÜLTESİ</t>
-  </si>
-  <si>
-    <t>FİZİK (İNGİLİZCE) - ÖRGÜN ÖĞRETİM</t>
-  </si>
-  <si>
-    <t>3.25 / 4.0</t>
-  </si>
-  <si>
-    <t>Mezun Kaydı Bulunamadı !!!</t>
+    <t xml:space="preserve">TC KIMLIK NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOYAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEZUNIYET TARIHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSITE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENSMYOFAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROGRAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DURUMU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKTAŞ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/01/2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İSTANBUL TEKNİK ÜNİVERSİTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELEKTRİK-ELEKTRONİK FAKÜLTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELEKTRONİK VE HABERLEŞME MÜHENDİSLİĞİ (İNGİLİZCE) - ÖRGÜN ÖĞRETİM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54 / 4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAYDI SİLİNMİŞTİR. (AYRILAN ÖĞRENCİLER) - MEZUNİYET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/06/2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOĞAZİÇİ ÜNİVERSİTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEN-EDEBİYAT FAKÜLTESİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FİZİK (İNGİLİZCE) (DR) - ÖRGÜN ÖĞRETİM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25 / 4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezun Kaydı Bulunamadı !!!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,7 +130,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -133,79 +138,99 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -258,127 +283,130 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="9.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="43.5703125" customWidth="1"/>
-    <col min="6" max="6" width="46.28515625" customWidth="1"/>
-    <col min="7" max="7" width="77.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="58.5703125" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="43.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="77.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="58.57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
         <v>58036147206</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="0" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
         <v>58036147206</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="0" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
         <v>64876364734</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>